--- a/Danza_Chic_V3_Excel_Formulas.xlsx
+++ b/Danza_Chic_V3_Excel_Formulas.xlsx
@@ -8,16 +8,22 @@
   </bookViews>
   <sheets>
     <sheet name="Índice" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Datos Internos" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Modelo Financiero" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Auditoría Capacidad" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Análisis Abandono" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Satisfacción NPS" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="DAFO" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Canales" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Experimentos" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Árbol Decisión" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="Cuadro Mando" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Estado Resultados" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Embudo Comercial" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Análisis Cohortes" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Calendario Anual" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Riesgos Operativos" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Ventaja Competitiva" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Datos Internos" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Modelo Financiero" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Auditoría Capacidad" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Análisis Abandono" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Satisfacción NPS" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="DAFO" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="Canales" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="Experimentos" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="Árbol Decisión" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="Cuadro Mando" sheetId="17" state="visible" r:id="rId17"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -30,7 +36,7 @@
     <numFmt numFmtId="164" formatCode="$#,##0"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="13">
+  <fonts count="16">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -102,8 +108,24 @@
       <name val="Courier New"/>
       <sz val="9"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <i val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00008000"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="9">
+  <fills count="12">
     <fill>
       <patternFill/>
     </fill>
@@ -152,6 +174,24 @@
         <bgColor rgb="00FFC000"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFE699"/>
+        <bgColor rgb="00FFE699"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DDEBF7"/>
+        <bgColor rgb="00DDEBF7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6E0B4"/>
+        <bgColor rgb="00C6E0B4"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -171,7 +211,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -216,6 +256,16 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="8" fillId="10" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="8" fillId="11" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="8" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -745,6 +795,995 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:D17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="35" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>BLOQUE 4: AUDITORÍA DE CAPACIDAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="7" t="inlineStr">
+        <is>
+          <t>Métrica</t>
+        </is>
+      </c>
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>Valor actual</t>
+        </is>
+      </c>
+      <c r="C3" s="7" t="inlineStr">
+        <is>
+          <t>Capacidad máxima</t>
+        </is>
+      </c>
+      <c r="D3" s="7" t="inlineStr">
+        <is>
+          <t>Ocupación (%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="13" t="inlineStr">
+        <is>
+          <t>Alumnas por clase (promedio)</t>
+        </is>
+      </c>
+      <c r="B5" s="17" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="13" t="inlineStr">
+        <is>
+          <t>Clases por día</t>
+        </is>
+      </c>
+      <c r="B6" s="17" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="13" t="inlineStr">
+        <is>
+          <t>Días abiertos por semana</t>
+        </is>
+      </c>
+      <c r="B7" s="17" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="13" t="inlineStr">
+        <is>
+          <t>Capacidad teórica total (alumnas)</t>
+        </is>
+      </c>
+      <c r="B8" s="18">
+        <f>B5*B6*B7</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="13" t="inlineStr">
+        <is>
+          <t>Alumnas actuales</t>
+        </is>
+      </c>
+      <c r="B9" s="17" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="13" t="inlineStr">
+        <is>
+          <t>OCUPACIÓN ACTUAL (%)</t>
+        </is>
+      </c>
+      <c r="B10" s="18">
+        <f>IF(B8=0,0,B9/B8)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="19" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>UMBRALES DE OCUPACIÓN</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>&gt;80%</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Verde</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Considerar ampliar horarios o local</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>60-80%</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Amarillo</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Optimizar horarios, marketing focalizado</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>&lt;60%</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Rojo</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Revisar precio, producto o captación</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A14:D14"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D26"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="35" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="35" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>BLOQUE 5: ANÁLISIS DE ABANDONO</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="20" t="inlineStr">
+        <is>
+          <t>5.1 MOTIVOS DE ABANDONO (Encuesta a madres)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>Motivo</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>% del total</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>Acción sugerida</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="13" t="inlineStr">
+        <is>
+          <t>Precio</t>
+        </is>
+      </c>
+      <c r="B5" s="21" t="n"/>
+      <c r="C5" s="13" t="inlineStr">
+        <is>
+          <t>Revisar precio, crear plan de pagos</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="13" t="inlineStr">
+        <is>
+          <t>Cambio de colegio</t>
+        </is>
+      </c>
+      <c r="B6" s="21" t="n"/>
+      <c r="C6" s="13" t="inlineStr">
+        <is>
+          <t>Nada (factor externo)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="13" t="inlineStr">
+        <is>
+          <t>Falta de interés de la niña</t>
+        </is>
+      </c>
+      <c r="B7" s="21" t="n"/>
+      <c r="C7" s="13" t="inlineStr">
+        <is>
+          <t>Revisar metodología, añadir variedad</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="13" t="inlineStr">
+        <is>
+          <t>Lesión</t>
+        </is>
+      </c>
+      <c r="B8" s="21" t="n"/>
+      <c r="C8" s="13" t="inlineStr">
+        <is>
+          <t>Revisar protocolo de calentamiento</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="13" t="inlineStr">
+        <is>
+          <t>Horarios incompatibles</t>
+        </is>
+      </c>
+      <c r="B9" s="21" t="n"/>
+      <c r="C9" s="13" t="inlineStr">
+        <is>
+          <t>PRIORIDAD #1: Abrir horarios alternativos</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="13" t="inlineStr">
+        <is>
+          <t>Cambio de ciudad</t>
+        </is>
+      </c>
+      <c r="B10" s="21" t="n"/>
+      <c r="C10" s="13" t="inlineStr">
+        <is>
+          <t>Nada (factor externo)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="13" t="inlineStr">
+        <is>
+          <t>Otra actividad (fútbol, natación)</t>
+        </is>
+      </c>
+      <c r="B11" s="21" t="n"/>
+      <c r="C11" s="13" t="inlineStr">
+        <is>
+          <t>Analizar qué ofrecen esas actividades</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="13" t="inlineStr">
+        <is>
+          <t>Insatisfacción con la enseñanza</t>
+        </is>
+      </c>
+      <c r="B12" s="21" t="n"/>
+      <c r="C12" s="13" t="inlineStr">
+        <is>
+          <t>Revisar metodología</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="13" t="inlineStr">
+        <is>
+          <t>Problemas familiares/económicos</t>
+        </is>
+      </c>
+      <c r="B13" s="21" t="n"/>
+      <c r="C13" s="13" t="inlineStr">
+        <is>
+          <t>Ofrecer plan de emergencia</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="13" t="inlineStr">
+        <is>
+          <t>No especificado</t>
+        </is>
+      </c>
+      <c r="B14" s="21" t="n"/>
+      <c r="C14" s="13" t="inlineStr">
+        <is>
+          <t>Llamar personalmente a cada familia</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="20" t="inlineStr">
+        <is>
+          <t>5.2 TASA DE ABANDONO MENSUAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>Mes</t>
+        </is>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>Alumnas inicio</t>
+        </is>
+      </c>
+      <c r="C18" s="7" t="inlineStr">
+        <is>
+          <t>Alumnas abandonan</t>
+        </is>
+      </c>
+      <c r="D18" s="7" t="inlineStr">
+        <is>
+          <t>Tasa (%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="13" t="inlineStr">
+        <is>
+          <t>Mes 1</t>
+        </is>
+      </c>
+      <c r="B19" s="22" t="n"/>
+      <c r="C19" s="22" t="n"/>
+      <c r="D19" s="23">
+        <f>IF(B19=0,0,C19/B19)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="13" t="inlineStr">
+        <is>
+          <t>Mes 2</t>
+        </is>
+      </c>
+      <c r="B20" s="22" t="n"/>
+      <c r="C20" s="22" t="n"/>
+      <c r="D20" s="23">
+        <f>IF(B20=0,0,C20/B20)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="13" t="inlineStr">
+        <is>
+          <t>Mes 3</t>
+        </is>
+      </c>
+      <c r="B21" s="22" t="n"/>
+      <c r="C21" s="22" t="n"/>
+      <c r="D21" s="23">
+        <f>IF(B21=0,0,C21/B21)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="13" t="inlineStr">
+        <is>
+          <t>Mes 4</t>
+        </is>
+      </c>
+      <c r="B22" s="22" t="n"/>
+      <c r="C22" s="22" t="n"/>
+      <c r="D22" s="23">
+        <f>IF(B22=0,0,C22/B22)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="13" t="inlineStr">
+        <is>
+          <t>Mes 5</t>
+        </is>
+      </c>
+      <c r="B23" s="22" t="n"/>
+      <c r="C23" s="22" t="n"/>
+      <c r="D23" s="23">
+        <f>IF(B23=0,0,C23/B23)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="13" t="inlineStr">
+        <is>
+          <t>Mes 6</t>
+        </is>
+      </c>
+      <c r="B24" s="22" t="n"/>
+      <c r="C24" s="22" t="n"/>
+      <c r="D24" s="23">
+        <f>IF(B24=0,0,C24/B24)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="24" t="inlineStr">
+        <is>
+          <t>⚠️ UMBRAL CRÍTICO: &gt;15% abandono mensual = producto defectuoso</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A26:C26"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="A17:C17"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="35" customWidth="1" min="1" max="1"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>BLOQUE 6: SATISFACCIÓN DEL CLIENTE</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="20" t="inlineStr">
+        <is>
+          <t>NPS (NET PROMOTER SCORE) — ENCUESTA TRIMESTRAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>Respuesta</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>Categoría</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>Cantidad</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="13" t="inlineStr">
+        <is>
+          <t>0-6</t>
+        </is>
+      </c>
+      <c r="B6" s="13" t="inlineStr">
+        <is>
+          <t>Detractora</t>
+        </is>
+      </c>
+      <c r="C6" s="13" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="13" t="inlineStr">
+        <is>
+          <t>7-8</t>
+        </is>
+      </c>
+      <c r="B7" s="25" t="inlineStr">
+        <is>
+          <t>Pasiva</t>
+        </is>
+      </c>
+      <c r="C7" s="13" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="13" t="inlineStr">
+        <is>
+          <t>9-10</t>
+        </is>
+      </c>
+      <c r="B8" s="25" t="inlineStr">
+        <is>
+          <t>Promotora</t>
+        </is>
+      </c>
+      <c r="C8" s="13" t="n"/>
+    </row>
+    <row r="9">
+      <c r="B9" s="26" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="20" t="inlineStr">
+        <is>
+          <t>NPS = % Promotoras - % Detractoras</t>
+        </is>
+      </c>
+      <c r="B10" s="27">
+        <f>(B9/(B7+B8+B9))-(B7/(B7+B8+B9))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="24" t="inlineStr">
+        <is>
+          <t>⚠️ UMBRAL: NPS &gt; 50 = excelente | NPS &lt; 30 = revisar urgente</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="20" t="inlineStr">
+        <is>
+          <t>TESTIMONIOS RECOPILADOS</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>Fecha</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>Testimonio (iniciales)</t>
+        </is>
+      </c>
+      <c r="C16" s="7" t="inlineStr">
+        <is>
+          <t>Usado en marketing</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="22" t="n"/>
+      <c r="B17" s="22" t="n"/>
+      <c r="C17" s="22" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="22" t="n"/>
+      <c r="B18" s="22" t="n"/>
+      <c r="C18" s="22" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="22" t="n"/>
+      <c r="B19" s="22" t="n"/>
+      <c r="C19" s="22" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="22" t="n"/>
+      <c r="B20" s="22" t="n"/>
+      <c r="C20" s="22" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="22" t="n"/>
+      <c r="B21" s="22" t="n"/>
+      <c r="C21" s="22" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="A15:C15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="50" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>BLOQUE 9: ANÁLISIS DAFO</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="28" t="inlineStr">
+        <is>
+          <t>FORTALEZAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="29" t="inlineStr">
+        <is>
+          <t>DEBILIDADES</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="30" t="inlineStr">
+        <is>
+          <t>OPORTUNIDADES</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="31" t="inlineStr">
+        <is>
+          <t>AMENAZAS</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="A3:B3"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="35" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>BLOQUE 11: CANALES DE ADQUISICIÓN</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="7" t="inlineStr">
+        <is>
+          <t>Canal</t>
+        </is>
+      </c>
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>Fuerza en Mérida</t>
+        </is>
+      </c>
+      <c r="C3" s="7" t="inlineStr">
+        <is>
+          <t>¿Cómo medir?</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="13" t="inlineStr">
+        <is>
+          <t>Recomendación madre-madre</t>
+        </is>
+      </c>
+      <c r="B4" s="13" t="inlineStr">
+        <is>
+          <t>🔴 ALTA</t>
+        </is>
+      </c>
+      <c r="C4" s="13" t="inlineStr">
+        <is>
+          <t>Encuesta: ¿Cómo se enteró?</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="13" t="inlineStr">
+        <is>
+          <t>Colegios</t>
+        </is>
+      </c>
+      <c r="B5" s="13" t="inlineStr">
+        <is>
+          <t>🔴 ALTA</t>
+        </is>
+      </c>
+      <c r="C5" s="13" t="inlineStr">
+        <is>
+          <t>¿Alianzas activas? ¿Panfletos?</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="13" t="inlineStr">
+        <is>
+          <t>Grupos WhatsApp de padres</t>
+        </is>
+      </c>
+      <c r="B6" s="13" t="inlineStr">
+        <is>
+          <t>🔴 ALTA</t>
+        </is>
+      </c>
+      <c r="C6" s="13" t="inlineStr">
+        <is>
+          <t>¿Aparece en conversaciones?</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="13" t="inlineStr">
+        <is>
+          <t>Instagram local</t>
+        </is>
+      </c>
+      <c r="B7" s="13" t="inlineStr">
+        <is>
+          <t>🟡 MEDIA</t>
+        </is>
+      </c>
+      <c r="C7" s="13" t="inlineStr">
+        <is>
+          <t>Seguidores, interacción, DMs</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="13" t="inlineStr">
+        <is>
+          <t>Eventos gratuitos / muestras</t>
+        </is>
+      </c>
+      <c r="B8" s="13" t="inlineStr">
+        <is>
+          <t>🟡 MEDIA</t>
+        </is>
+      </c>
+      <c r="C8" s="13" t="inlineStr">
+        <is>
+          <t>Asistencia, conversión</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="13" t="inlineStr">
+        <is>
+          <t>Meta Ads pagadas</t>
+        </is>
+      </c>
+      <c r="B9" s="13" t="inlineStr">
+        <is>
+          <t>🟢 BAJA</t>
+        </is>
+      </c>
+      <c r="C9" s="13" t="inlineStr">
+        <is>
+          <t>CAC probablemente &gt; LTV</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="13" t="inlineStr">
+        <is>
+          <t>Pasear por el local</t>
+        </is>
+      </c>
+      <c r="B10" s="13" t="inlineStr">
+        <is>
+          <t>🟢 BAJA-MEDIA</t>
+        </is>
+      </c>
+      <c r="C10" s="13" t="inlineStr">
+        <is>
+          <t>¿Cuántos entran por el letrero?</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:C1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="35" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>BLOQUE 12: EXPERIMENTOS DE VALIDACIÓN</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>Exp 1: Observación competencia</t>
+        </is>
+      </c>
+      <c r="B3" s="13" t="inlineStr">
+        <is>
+          <t>0 USD, 3-4 días</t>
+        </is>
+      </c>
+      <c r="C3" s="13" t="inlineStr">
+        <is>
+          <t>Contar entradas en Nueva Danza y Agbara</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="13" t="inlineStr">
+        <is>
+          <t>Exp 2: Entrevistas interceptación</t>
+        </is>
+      </c>
+      <c r="B4" s="13" t="inlineStr">
+        <is>
+          <t>0 USD, 3-5 días</t>
+        </is>
+      </c>
+      <c r="C4" s="13" t="inlineStr">
+        <is>
+          <t>Objetivo: 20+ contactos WhatsApp</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="13" t="inlineStr">
+        <is>
+          <t>Exp 3: Test de precio</t>
+        </is>
+      </c>
+      <c r="B5" s="13" t="inlineStr">
+        <is>
+          <t>Interno</t>
+        </is>
+      </c>
+      <c r="C5" s="13" t="inlineStr">
+        <is>
+          <t>Subir 10-15% a nuevas. ¿Baja conversión?</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="13" t="inlineStr">
+        <is>
+          <t>Exp 4: Oferta premium (Danza Chic Elite)</t>
+        </is>
+      </c>
+      <c r="B6" s="13" t="inlineStr">
+        <is>
+          <t>0 USD</t>
+        </is>
+      </c>
+      <c r="C6" s="13" t="inlineStr">
+        <is>
+          <t>Medir % familias que pagan upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="13" t="inlineStr">
+        <is>
+          <t>Exp 5: Sistema de referidos</t>
+        </is>
+      </c>
+      <c r="B7" s="13" t="inlineStr">
+        <is>
+          <t>Costo bajo</t>
+        </is>
+      </c>
+      <c r="C7" s="13" t="inlineStr">
+        <is>
+          <t>1 semana gratis por referida</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="13" t="inlineStr">
+        <is>
+          <t>Exp 6: Pop-up (MVP)</t>
+        </is>
+      </c>
+      <c r="B8" s="13" t="inlineStr">
+        <is>
+          <t>100-300 USD</t>
+        </is>
+      </c>
+      <c r="C8" s="13" t="inlineStr">
+        <is>
+          <t>Alquilar sala 8 semanas. Objetivo: 30 alumnas</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:C1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:A19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -885,7 +1924,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1203,6 +2242,1678 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:F32"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>ESTADO DE RESULTADOS MENSUAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="34" t="inlineStr">
+        <is>
+          <t>Registrar los números reales cada mes</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>Concepto</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>Mes 1</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>Mes 2</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>Mes 3</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>Mes 4</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>Promedio</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="20" t="inlineStr">
+        <is>
+          <t>INGRESOS</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Matrícula (alumnas × precio)</t>
+        </is>
+      </c>
+      <c r="B6" s="13" t="n"/>
+      <c r="C6" s="13" t="n"/>
+      <c r="D6" s="13" t="n"/>
+      <c r="E6" s="13" t="n"/>
+      <c r="F6" s="13" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Otros ingresos (eventos, privadas)</t>
+        </is>
+      </c>
+      <c r="B7" s="13" t="n"/>
+      <c r="C7" s="13" t="n"/>
+      <c r="D7" s="13" t="n"/>
+      <c r="E7" s="13" t="n"/>
+      <c r="F7" s="13" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="35" t="inlineStr">
+        <is>
+          <t>TOTAL INGRESOS</t>
+        </is>
+      </c>
+      <c r="B8" s="36" t="n"/>
+      <c r="C8" s="36" t="n"/>
+      <c r="D8" s="36" t="n"/>
+      <c r="E8" s="36" t="n"/>
+      <c r="F8" s="36" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="20" t="inlineStr">
+        <is>
+          <t>GASTOS VARIABLES</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Uniformes y material</t>
+        </is>
+      </c>
+      <c r="B11" s="22" t="n"/>
+      <c r="C11" s="22" t="n"/>
+      <c r="D11" s="22" t="n"/>
+      <c r="E11" s="22" t="n"/>
+      <c r="F11" s="22" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Servicios extra (agua, electricidad)</t>
+        </is>
+      </c>
+      <c r="B12" s="22" t="n"/>
+      <c r="C12" s="22" t="n"/>
+      <c r="D12" s="22" t="n"/>
+      <c r="E12" s="22" t="n"/>
+      <c r="F12" s="22" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Comisiones o descuentos</t>
+        </is>
+      </c>
+      <c r="B13" s="22" t="n"/>
+      <c r="C13" s="22" t="n"/>
+      <c r="D13" s="22" t="n"/>
+      <c r="E13" s="22" t="n"/>
+      <c r="F13" s="22" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="35" t="inlineStr">
+        <is>
+          <t>TOTAL GASTOS VARIABLES</t>
+        </is>
+      </c>
+      <c r="B14" s="37" t="n"/>
+      <c r="C14" s="37" t="n"/>
+      <c r="D14" s="37" t="n"/>
+      <c r="E14" s="37" t="n"/>
+      <c r="F14" s="37" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="38" t="inlineStr">
+        <is>
+          <t>MARGEN BRUTO (Ingresos - Gastos variables)</t>
+        </is>
+      </c>
+      <c r="B16" s="12">
+        <f>B9-B13</f>
+        <v/>
+      </c>
+      <c r="C16" s="12">
+        <f>C9-C13</f>
+        <v/>
+      </c>
+      <c r="D16" s="12">
+        <f>D9-D13</f>
+        <v/>
+      </c>
+      <c r="E16" s="12">
+        <f>E9-E13</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="20" t="inlineStr">
+        <is>
+          <t>GASTOS FIJOS</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Alquiler local</t>
+        </is>
+      </c>
+      <c r="B19" s="22" t="n"/>
+      <c r="C19" s="22" t="n"/>
+      <c r="D19" s="22" t="n"/>
+      <c r="E19" s="22" t="n"/>
+      <c r="F19" s="22" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Profesor (si contratado)</t>
+        </is>
+      </c>
+      <c r="B20" s="22" t="n"/>
+      <c r="C20" s="22" t="n"/>
+      <c r="D20" s="22" t="n"/>
+      <c r="E20" s="22" t="n"/>
+      <c r="F20" s="22" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="B21" s="22" t="n"/>
+      <c r="C21" s="22" t="n"/>
+      <c r="D21" s="22" t="n"/>
+      <c r="E21" s="22" t="n"/>
+      <c r="F21" s="22" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Servicios (teléfono, internet)</t>
+        </is>
+      </c>
+      <c r="B22" s="22" t="n"/>
+      <c r="C22" s="22" t="n"/>
+      <c r="D22" s="22" t="n"/>
+      <c r="E22" s="22" t="n"/>
+      <c r="F22" s="22" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Seguros</t>
+        </is>
+      </c>
+      <c r="B23" s="22" t="n"/>
+      <c r="C23" s="22" t="n"/>
+      <c r="D23" s="22" t="n"/>
+      <c r="E23" s="22" t="n"/>
+      <c r="F23" s="22" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="35" t="inlineStr">
+        <is>
+          <t>TOTAL GASTOS FIJOS</t>
+        </is>
+      </c>
+      <c r="B24" s="37" t="n"/>
+      <c r="C24" s="37" t="n"/>
+      <c r="D24" s="37" t="n"/>
+      <c r="E24" s="37" t="n"/>
+      <c r="F24" s="37" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="20" t="inlineStr">
+        <is>
+          <t>RESULTADO OPERATIVO (MARGEN BRUTO - GASTOS FIJOS)</t>
+        </is>
+      </c>
+      <c r="B26" s="39">
+        <f>B14-B24</f>
+        <v/>
+      </c>
+      <c r="C26" s="39">
+        <f>C14-C24</f>
+        <v/>
+      </c>
+      <c r="D26" s="39">
+        <f>D14-D24</f>
+        <v/>
+      </c>
+      <c r="E26" s="39">
+        <f>E14-E24</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>FLUJO DE CAJA (Simplificado)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>Saldo anterior</t>
+        </is>
+      </c>
+      <c r="B29" s="40" t="n"/>
+      <c r="C29" s="40" t="n"/>
+      <c r="D29" s="40" t="n"/>
+      <c r="E29" s="40" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>+ Ingresos del mes</t>
+        </is>
+      </c>
+      <c r="B30" s="12">
+        <f>B9</f>
+        <v/>
+      </c>
+      <c r="C30" s="12">
+        <f>C9</f>
+        <v/>
+      </c>
+      <c r="D30" s="12">
+        <f>D9</f>
+        <v/>
+      </c>
+      <c r="E30" s="12">
+        <f>E9</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>- Gastos del mes (variable + fijo)</t>
+        </is>
+      </c>
+      <c r="B31" s="12">
+        <f>B13+B24</f>
+        <v/>
+      </c>
+      <c r="C31" s="12">
+        <f>C13+C24</f>
+        <v/>
+      </c>
+      <c r="D31" s="12">
+        <f>D13+D24</f>
+        <v/>
+      </c>
+      <c r="E31" s="12">
+        <f>E13+E24</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="35">
+        <f> SALDO FINAL DEL MES</f>
+        <v/>
+      </c>
+      <c r="B32" s="41">
+        <f>B29+B30-B31</f>
+        <v/>
+      </c>
+      <c r="C32" s="41">
+        <f>C29+C30-C31</f>
+        <v/>
+      </c>
+      <c r="D32" s="41">
+        <f>D29+D30-D31</f>
+        <v/>
+      </c>
+      <c r="E32" s="41">
+        <f>E29+E30-E31</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A10:F10"/>
+    <mergeCell ref="A28:F28"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="A16"/>
+    <mergeCell ref="A18:F18"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F18"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="35" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>EMBUDO COMERCIAL (SALES FUNNEL)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="34" t="inlineStr">
+        <is>
+          <t>Dónde se pierde cada persona del proceso de venta</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>Etapa</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>Mes 1</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>Mes 2</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>Mes 3</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>% Conversión</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>Notas</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="13" t="inlineStr">
+        <is>
+          <t>1️⃣ Personas que preguntan</t>
+        </is>
+      </c>
+      <c r="B5" s="22" t="n"/>
+      <c r="C5" s="22" t="n"/>
+      <c r="D5" s="22" t="n"/>
+      <c r="E5" s="13" t="n"/>
+      <c r="F5" s="13" t="inlineStr">
+        <is>
+          <t>Contactos WhatsApp o llamadas</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="13" t="inlineStr">
+        <is>
+          <t>2️⃣ Asisten a clase de prueba</t>
+        </is>
+      </c>
+      <c r="B6" s="22" t="n"/>
+      <c r="C6" s="22" t="n"/>
+      <c r="D6" s="22" t="n"/>
+      <c r="E6" s="23">
+        <f>IF(B5=0,0,B6/B5)</f>
+        <v/>
+      </c>
+      <c r="F6" s="13" t="inlineStr">
+        <is>
+          <t>Objetivo: medir cada etapa</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="13" t="inlineStr">
+        <is>
+          <t>3️⃣ Se matriculan (mes 1)</t>
+        </is>
+      </c>
+      <c r="B7" s="22" t="n"/>
+      <c r="C7" s="22" t="n"/>
+      <c r="D7" s="22" t="n"/>
+      <c r="E7" s="23">
+        <f>IF(B6=0,0,B7/B6)</f>
+        <v/>
+      </c>
+      <c r="F7" s="13" t="inlineStr">
+        <is>
+          <t>Objetivo: medir cada etapa</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="13" t="inlineStr">
+        <is>
+          <t>4️⃣ Renuevan mes 2</t>
+        </is>
+      </c>
+      <c r="B8" s="22" t="n"/>
+      <c r="C8" s="22" t="n"/>
+      <c r="D8" s="22" t="n"/>
+      <c r="E8" s="23">
+        <f>IF(B7=0,0,B8/B7)</f>
+        <v/>
+      </c>
+      <c r="F8" s="13" t="inlineStr">
+        <is>
+          <t>Objetivo: medir cada etapa</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="13" t="inlineStr">
+        <is>
+          <t>5️⃣ Permanecen mes 6</t>
+        </is>
+      </c>
+      <c r="B9" s="22" t="n"/>
+      <c r="C9" s="22" t="n"/>
+      <c r="D9" s="22" t="n"/>
+      <c r="E9" s="23">
+        <f>IF(B8=0,0,B9/B8)</f>
+        <v/>
+      </c>
+      <c r="F9" s="13" t="inlineStr">
+        <is>
+          <t>Objetivo: medir cada etapa</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="13" t="inlineStr">
+        <is>
+          <t>6️⃣ Se convierten en referidos</t>
+        </is>
+      </c>
+      <c r="B10" s="22" t="n"/>
+      <c r="C10" s="22" t="n"/>
+      <c r="D10" s="22" t="n"/>
+      <c r="E10" s="23">
+        <f>IF(B9=0,0,B10/B9)</f>
+        <v/>
+      </c>
+      <c r="F10" s="13" t="inlineStr">
+        <is>
+          <t>Objetivo: medir cada etapa</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="20" t="inlineStr">
+        <is>
+          <t>CONVERSIÓN CRÍTICA POR ETAPA</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="13" t="inlineStr">
+        <is>
+          <t>Pregunta → Prueba</t>
+        </is>
+      </c>
+      <c r="B14" s="13" t="inlineStr">
+        <is>
+          <t>&gt;60%</t>
+        </is>
+      </c>
+      <c r="C14" s="13" t="inlineStr">
+        <is>
+          <t>Si &lt;60%: interés débil o precio muy alto</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="13" t="inlineStr">
+        <is>
+          <t>Prueba → Matrícula</t>
+        </is>
+      </c>
+      <c r="B15" s="13" t="inlineStr">
+        <is>
+          <t>&gt;40%</t>
+        </is>
+      </c>
+      <c r="C15" s="13" t="inlineStr">
+        <is>
+          <t>Si &lt;40%: producto/experiencia defectuosos</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="13" t="inlineStr">
+        <is>
+          <t>Mes 1 → Mes 2</t>
+        </is>
+      </c>
+      <c r="B16" s="13" t="inlineStr">
+        <is>
+          <t>&gt;80%</t>
+        </is>
+      </c>
+      <c r="C16" s="13" t="inlineStr">
+        <is>
+          <t>Si &lt;80%: problema en primeras clases o precio</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="13" t="inlineStr">
+        <is>
+          <t>Mes 1 → Mes 6</t>
+        </is>
+      </c>
+      <c r="B17" s="13" t="inlineStr">
+        <is>
+          <t>&gt;60%</t>
+        </is>
+      </c>
+      <c r="C17" s="13" t="inlineStr">
+        <is>
+          <t>Si &lt;60%: falta de motivación de alumna o falta de progreso visible</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="13" t="inlineStr">
+        <is>
+          <t>Matrícula → Referidos</t>
+        </is>
+      </c>
+      <c r="B18" s="13" t="inlineStr">
+        <is>
+          <t>&gt;30%</t>
+        </is>
+      </c>
+      <c r="C18" s="13" t="inlineStr">
+        <is>
+          <t>Si &lt;30%: no hay satisfacción suficiente</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A13:F13"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>ANÁLISIS DE COHORTES</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="34" t="inlineStr">
+        <is>
+          <t>Retención de grupos de alumnas por mes de ingreso</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>Mes Ingreso</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>Mes 1</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>Mes 2</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>Mes 3</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>Mes 4</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>Mes 5</t>
+        </is>
+      </c>
+      <c r="G4" s="7" t="inlineStr">
+        <is>
+          <t>Mes 6</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Cohorte Mes 1</t>
+        </is>
+      </c>
+      <c r="B5" s="22" t="n"/>
+      <c r="C5" s="22" t="n"/>
+      <c r="D5" s="22" t="n"/>
+      <c r="E5" s="22" t="n"/>
+      <c r="F5" s="22" t="n"/>
+      <c r="G5" s="22" t="n"/>
+      <c r="H5" s="22" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Cohorte Mes 2</t>
+        </is>
+      </c>
+      <c r="B6" s="22" t="n"/>
+      <c r="C6" s="22" t="n"/>
+      <c r="D6" s="22" t="n"/>
+      <c r="E6" s="22" t="n"/>
+      <c r="F6" s="22" t="n"/>
+      <c r="G6" s="22" t="n"/>
+      <c r="H6" s="22" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Cohorte Mes 3</t>
+        </is>
+      </c>
+      <c r="B7" s="22" t="n"/>
+      <c r="C7" s="22" t="n"/>
+      <c r="D7" s="22" t="n"/>
+      <c r="E7" s="22" t="n"/>
+      <c r="F7" s="22" t="n"/>
+      <c r="G7" s="22" t="n"/>
+      <c r="H7" s="22" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Cohorte Mes 4</t>
+        </is>
+      </c>
+      <c r="B8" s="22" t="n"/>
+      <c r="C8" s="22" t="n"/>
+      <c r="D8" s="22" t="n"/>
+      <c r="E8" s="22" t="n"/>
+      <c r="F8" s="22" t="n"/>
+      <c r="G8" s="22" t="n"/>
+      <c r="H8" s="22" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Cohorte Mes 5</t>
+        </is>
+      </c>
+      <c r="B9" s="22" t="n"/>
+      <c r="C9" s="22" t="n"/>
+      <c r="D9" s="22" t="n"/>
+      <c r="E9" s="22" t="n"/>
+      <c r="F9" s="22" t="n"/>
+      <c r="G9" s="22" t="n"/>
+      <c r="H9" s="22" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Cohorte Mes 6</t>
+        </is>
+      </c>
+      <c r="B10" s="22" t="n"/>
+      <c r="C10" s="22" t="n"/>
+      <c r="D10" s="22" t="n"/>
+      <c r="E10" s="22" t="n"/>
+      <c r="F10" s="22" t="n"/>
+      <c r="G10" s="22" t="n"/>
+      <c r="H10" s="22" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="35" t="inlineStr">
+        <is>
+          <t>Retención promedio (%)</t>
+        </is>
+      </c>
+      <c r="B12" s="27">
+        <f>IF(COUNT(B6:B11)=0,0,AVERAGE(B6:B11))</f>
+        <v/>
+      </c>
+      <c r="C12" s="27">
+        <f>IF(COUNT(C6:C11)=0,0,AVERAGE(C6:C11))</f>
+        <v/>
+      </c>
+      <c r="D12" s="27">
+        <f>IF(COUNT(D6:D11)=0,0,AVERAGE(D6:D11))</f>
+        <v/>
+      </c>
+      <c r="E12" s="27">
+        <f>IF(COUNT(E6:E11)=0,0,AVERAGE(E6:E11))</f>
+        <v/>
+      </c>
+      <c r="F12" s="27">
+        <f>IF(COUNT(F6:F11)=0,0,AVERAGE(F6:F11))</f>
+        <v/>
+      </c>
+      <c r="G12" s="27">
+        <f>IF(COUNT(G6:G11)=0,0,AVERAGE(G6:G11))</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A1:G1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>CALENDARIO ANUAL OPERATIVO</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="34" t="inlineStr">
+        <is>
+          <t>Contexto estacional para interpretar datos</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>Mes</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>Período</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>Contexto</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>Acciones</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>Métrica clave</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="13" t="inlineStr">
+        <is>
+          <t>Enero</t>
+        </is>
+      </c>
+      <c r="B5" s="13" t="inlineStr">
+        <is>
+          <t>Año nuevo</t>
+        </is>
+      </c>
+      <c r="C5" s="13" t="inlineStr">
+        <is>
+          <t>Captación alta (nuevas rutinas)</t>
+        </is>
+      </c>
+      <c r="D5" s="13" t="inlineStr">
+        <is>
+          <t>Marketing, referidos</t>
+        </is>
+      </c>
+      <c r="E5" s="13" t="inlineStr">
+        <is>
+          <t>Nuevas matríc</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="13" t="inlineStr">
+        <is>
+          <t>Febrero-Marzo</t>
+        </is>
+      </c>
+      <c r="B6" s="13" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="C6" s="13" t="inlineStr">
+        <is>
+          <t>Retención temprana (riesgo abandono)</t>
+        </is>
+      </c>
+      <c r="D6" s="13" t="inlineStr">
+        <is>
+          <t>Retener, eventos</t>
+        </is>
+      </c>
+      <c r="E6" s="13" t="inlineStr">
+        <is>
+          <t>% Retención</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="13" t="inlineStr">
+        <is>
+          <t>Abril-Mayo</t>
+        </is>
+      </c>
+      <c r="B7" s="13" t="inlineStr">
+        <is>
+          <t>Pre-vacaciones</t>
+        </is>
+      </c>
+      <c r="C7" s="13" t="inlineStr">
+        <is>
+          <t>Estable</t>
+        </is>
+      </c>
+      <c r="D7" s="13" t="inlineStr">
+        <is>
+          <t>Mantener, preparar verano</t>
+        </is>
+      </c>
+      <c r="E7" s="13" t="inlineStr">
+        <is>
+          <t>Ocupación</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="13" t="inlineStr">
+        <is>
+          <t>Junio</t>
+        </is>
+      </c>
+      <c r="B8" s="13" t="inlineStr">
+        <is>
+          <t>Fin de año escolar</t>
+        </is>
+      </c>
+      <c r="C8" s="13" t="inlineStr">
+        <is>
+          <t>Fiestas de fin de año</t>
+        </is>
+      </c>
+      <c r="D8" s="13" t="inlineStr">
+        <is>
+          <t>Festival/gala</t>
+        </is>
+      </c>
+      <c r="E8" s="13" t="inlineStr">
+        <is>
+          <t>Satisfacción</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="13" t="inlineStr">
+        <is>
+          <t>Julio</t>
+        </is>
+      </c>
+      <c r="B9" s="13" t="inlineStr">
+        <is>
+          <t>Vacaciones escolares</t>
+        </is>
+      </c>
+      <c r="C9" s="13" t="inlineStr">
+        <is>
+          <t>Baja demanda, posible cierre</t>
+        </is>
+      </c>
+      <c r="D9" s="13" t="inlineStr">
+        <is>
+          <t>Campamento (opcional)</t>
+        </is>
+      </c>
+      <c r="E9" s="13" t="inlineStr">
+        <is>
+          <t>CAC</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="13" t="inlineStr">
+        <is>
+          <t>Agosto</t>
+        </is>
+      </c>
+      <c r="B10" s="13" t="inlineStr">
+        <is>
+          <t>Retorno escolar</t>
+        </is>
+      </c>
+      <c r="C10" s="13" t="inlineStr">
+        <is>
+          <t>Captación alta (vuelta a clases)</t>
+        </is>
+      </c>
+      <c r="D10" s="13" t="inlineStr">
+        <is>
+          <t>Marketing, re-inscrip</t>
+        </is>
+      </c>
+      <c r="E10" s="13" t="inlineStr">
+        <is>
+          <t>Conversión</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="13" t="inlineStr">
+        <is>
+          <t>Septiembre-Octubre</t>
+        </is>
+      </c>
+      <c r="B11" s="13" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="C11" s="13" t="inlineStr">
+        <is>
+          <t>Estable post-vacaciones</t>
+        </is>
+      </c>
+      <c r="D11" s="13" t="inlineStr">
+        <is>
+          <t>Consolidar alumnas</t>
+        </is>
+      </c>
+      <c r="E11" s="13" t="inlineStr">
+        <is>
+          <t>Ocupación</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="13" t="inlineStr">
+        <is>
+          <t>Noviembre-Diciembre</t>
+        </is>
+      </c>
+      <c r="B12" s="13" t="inlineStr">
+        <is>
+          <t>Festejos</t>
+        </is>
+      </c>
+      <c r="C12" s="13" t="inlineStr">
+        <is>
+          <t>Eventos, competiciones</t>
+        </is>
+      </c>
+      <c r="D12" s="13" t="inlineStr">
+        <is>
+          <t>Festival, navidad</t>
+        </is>
+      </c>
+      <c r="E12" s="13" t="inlineStr">
+        <is>
+          <t>NPS</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>ANÁLISIS DE RIESGOS OPERATIVOS</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="34" t="inlineStr">
+        <is>
+          <t>Contingencias y planes de mitigación</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>Riesgo</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>Impacto</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>Probabilidad</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>Prioridad</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>Plan de mitigación</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="13" t="inlineStr">
+        <is>
+          <t>Enfermedad profesora principal</t>
+        </is>
+      </c>
+      <c r="B5" s="13" t="inlineStr">
+        <is>
+          <t>Alto (80% ingresos dependen)</t>
+        </is>
+      </c>
+      <c r="C5" s="13" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="D5" s="13" t="inlineStr">
+        <is>
+          <t>🔴 CRÍTICO</t>
+        </is>
+      </c>
+      <c r="E5" s="13" t="inlineStr">
+        <is>
+          <t>Contratar backup</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="13" t="inlineStr">
+        <is>
+          <t>Pérdida del local (desalojo, cierre)</t>
+        </is>
+      </c>
+      <c r="B6" s="13" t="inlineStr">
+        <is>
+          <t>Alto</t>
+        </is>
+      </c>
+      <c r="C6" s="13" t="inlineStr">
+        <is>
+          <t>Baja pero real</t>
+        </is>
+      </c>
+      <c r="D6" s="13" t="inlineStr">
+        <is>
+          <t>🔴 CRÍTICO</t>
+        </is>
+      </c>
+      <c r="E6" s="13" t="inlineStr">
+        <is>
+          <t>Fondo de emergencia 3 meses alquiler</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="13" t="inlineStr">
+        <is>
+          <t>Ruptura alianza con colegio</t>
+        </is>
+      </c>
+      <c r="B7" s="13" t="inlineStr">
+        <is>
+          <t>Medio-Alto</t>
+        </is>
+      </c>
+      <c r="C7" s="13" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="D7" s="13" t="inlineStr">
+        <is>
+          <t>🟡 ALTO</t>
+        </is>
+      </c>
+      <c r="E7" s="13" t="inlineStr">
+        <is>
+          <t>Diversificar colegios (no 1 solo)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="13" t="inlineStr">
+        <is>
+          <t>Embargo/secuestro en Venezuela</t>
+        </is>
+      </c>
+      <c r="B8" s="13" t="inlineStr">
+        <is>
+          <t>Alto</t>
+        </is>
+      </c>
+      <c r="C8" s="13" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="D8" s="13" t="inlineStr">
+        <is>
+          <t>🔴 CRÍTICO</t>
+        </is>
+      </c>
+      <c r="E8" s="13" t="inlineStr">
+        <is>
+          <t>Fondo 6 meses en USD digital</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="13" t="inlineStr">
+        <is>
+          <t>Fuga de clientes a competidor</t>
+        </is>
+      </c>
+      <c r="B9" s="13" t="inlineStr">
+        <is>
+          <t>Medio</t>
+        </is>
+      </c>
+      <c r="C9" s="13" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="D9" s="13" t="inlineStr">
+        <is>
+          <t>🟡 ALTO</t>
+        </is>
+      </c>
+      <c r="E9" s="13" t="inlineStr">
+        <is>
+          <t>Mejorar experiencia, eventos</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="13" t="inlineStr">
+        <is>
+          <t>No renovación de alumnas (baja retención)</t>
+        </is>
+      </c>
+      <c r="B10" s="13" t="inlineStr">
+        <is>
+          <t>Medio-Alto</t>
+        </is>
+      </c>
+      <c r="C10" s="13" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="D10" s="13" t="inlineStr">
+        <is>
+          <t>🟡 ALTO</t>
+        </is>
+      </c>
+      <c r="E10" s="13" t="inlineStr">
+        <is>
+          <t>Medir NPS, mejorar servicio</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="13" t="inlineStr">
+        <is>
+          <t>Lesión alumna (demanda)</t>
+        </is>
+      </c>
+      <c r="B11" s="13" t="inlineStr">
+        <is>
+          <t>Bajo-Medio</t>
+        </is>
+      </c>
+      <c r="C11" s="13" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="D11" s="13" t="inlineStr">
+        <is>
+          <t>🟢 MEDIO</t>
+        </is>
+      </c>
+      <c r="E11" s="13" t="inlineStr">
+        <is>
+          <t>Seguro de responsabilidad civil</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="13" t="inlineStr">
+        <is>
+          <t>Falta de renovación de inscripción</t>
+        </is>
+      </c>
+      <c r="B12" s="13" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
+      <c r="C12" s="13" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="D12" s="13" t="inlineStr">
+        <is>
+          <t>🟢 MEDIO</t>
+        </is>
+      </c>
+      <c r="E12" s="13" t="inlineStr">
+        <is>
+          <t>Sistema de recordatorios automatizado</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>VENTAJA COMPETITIVA (ANÁLISIS PUNTUAL)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="34" t="inlineStr">
+        <is>
+          <t>¿Qué hace difícil de copiar a Danza Chic? Scoring de defensibilidad</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>¿La tiene?</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>Difícil de copiar?</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>Impacto (1-5)</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>Puntuación</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>Cómo fortalecerla</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="13" t="inlineStr">
+        <is>
+          <t>Metodología documentada</t>
+        </is>
+      </c>
+      <c r="B5" s="22" t="n"/>
+      <c r="C5" s="13" t="inlineStr">
+        <is>
+          <t>Alto</t>
+        </is>
+      </c>
+      <c r="D5" s="13" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E5" s="42">
+        <f>IF(D5="",0,VALUE(D5))</f>
+        <v/>
+      </c>
+      <c r="F5" s="13" t="inlineStr">
+        <is>
+          <t>Crear manual de procesos</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="13" t="inlineStr">
+        <is>
+          <t>Comunidad fuerte de padres</t>
+        </is>
+      </c>
+      <c r="B6" s="22" t="n"/>
+      <c r="C6" s="13" t="inlineStr">
+        <is>
+          <t>Alto</t>
+        </is>
+      </c>
+      <c r="D6" s="13" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E6" s="42">
+        <f>IF(D6="",0,VALUE(D6))</f>
+        <v/>
+      </c>
+      <c r="F6" s="13" t="inlineStr">
+        <is>
+          <t>Grupo WhatsApp + eventos privados</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="13" t="inlineStr">
+        <is>
+          <t>Eventos reconocidos (galas anuales)</t>
+        </is>
+      </c>
+      <c r="B7" s="22" t="n"/>
+      <c r="C7" s="13" t="inlineStr">
+        <is>
+          <t>Medio-Alto</t>
+        </is>
+      </c>
+      <c r="D7" s="13" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E7" s="42">
+        <f>IF(D7="",0,VALUE(D7))</f>
+        <v/>
+      </c>
+      <c r="F7" s="13" t="inlineStr">
+        <is>
+          <t>Participar en ferias locales</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="13" t="inlineStr">
+        <is>
+          <t>Alianzas exclusivas con colegios</t>
+        </is>
+      </c>
+      <c r="B8" s="22" t="n"/>
+      <c r="C8" s="13" t="inlineStr">
+        <is>
+          <t>Alto</t>
+        </is>
+      </c>
+      <c r="D8" s="13" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E8" s="42">
+        <f>IF(D8="",0,VALUE(D8))</f>
+        <v/>
+      </c>
+      <c r="F8" s="13" t="inlineStr">
+        <is>
+          <t>Contratos formales, no verbales</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="13" t="inlineStr">
+        <is>
+          <t>Marca consolidada (años)</t>
+        </is>
+      </c>
+      <c r="B9" s="22" t="n"/>
+      <c r="C9" s="13" t="inlineStr">
+        <is>
+          <t>Medio</t>
+        </is>
+      </c>
+      <c r="D9" s="13" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E9" s="42">
+        <f>IF(D9="",0,VALUE(D9))</f>
+        <v/>
+      </c>
+      <c r="F9" s="13" t="inlineStr">
+        <is>
+          <t>Registrar marca en SAPI</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="13" t="inlineStr">
+        <is>
+          <t>Reputación de la propietaria</t>
+        </is>
+      </c>
+      <c r="B10" s="22" t="n"/>
+      <c r="C10" s="13" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
+      <c r="D10" s="13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E10" s="42">
+        <f>IF(D10="",0,VALUE(D10))</f>
+        <v/>
+      </c>
+      <c r="F10" s="13" t="inlineStr">
+        <is>
+          <t>❌ Sustituir por ventajas estructurales</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="20" t="inlineStr">
+        <is>
+          <t>PUNTUACIÓN TOTAL</t>
+        </is>
+      </c>
+      <c r="E12" s="43">
+        <f>SUM(E5:E10)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>⚠️ Si "Reputación de propietaria" &gt; 50% de puntuación: el negocio NO ES DEFENDIBLE</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A13:F13"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:D22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -1509,7 +4220,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1805,993 +4516,4 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D17"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="35" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>BLOQUE 4: AUDITORÍA DE CAPACIDAD</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="7" t="inlineStr">
-        <is>
-          <t>Métrica</t>
-        </is>
-      </c>
-      <c r="B3" s="7" t="inlineStr">
-        <is>
-          <t>Valor actual</t>
-        </is>
-      </c>
-      <c r="C3" s="7" t="inlineStr">
-        <is>
-          <t>Capacidad máxima</t>
-        </is>
-      </c>
-      <c r="D3" s="7" t="inlineStr">
-        <is>
-          <t>Ocupación (%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="13" t="inlineStr">
-        <is>
-          <t>Alumnas por clase (promedio)</t>
-        </is>
-      </c>
-      <c r="B5" s="17" t="n"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="13" t="inlineStr">
-        <is>
-          <t>Clases por día</t>
-        </is>
-      </c>
-      <c r="B6" s="17" t="n"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="13" t="inlineStr">
-        <is>
-          <t>Días abiertos por semana</t>
-        </is>
-      </c>
-      <c r="B7" s="17" t="n"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="13" t="inlineStr">
-        <is>
-          <t>Capacidad teórica total (alumnas)</t>
-        </is>
-      </c>
-      <c r="B8" s="18">
-        <f>B5*B6*B7</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="13" t="inlineStr">
-        <is>
-          <t>Alumnas actuales</t>
-        </is>
-      </c>
-      <c r="B9" s="17" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="13" t="inlineStr">
-        <is>
-          <t>OCUPACIÓN ACTUAL (%)</t>
-        </is>
-      </c>
-      <c r="B10" s="18">
-        <f>IF(B8=0,0,B9/B8)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11">
-      <c r="B11" s="19" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t>UMBRALES DE OCUPACIÓN</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>&gt;80%</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Verde</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Considerar ampliar horarios o local</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>60-80%</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Amarillo</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Optimizar horarios, marketing focalizado</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>&lt;60%</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Rojo</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Revisar precio, producto o captación</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A14:D14"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D26"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="35" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="35" customWidth="1" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>BLOQUE 5: ANÁLISIS DE ABANDONO</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="20" t="inlineStr">
-        <is>
-          <t>5.1 MOTIVOS DE ABANDONO (Encuesta a madres)</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="7" t="inlineStr">
-        <is>
-          <t>Motivo</t>
-        </is>
-      </c>
-      <c r="B4" s="7" t="inlineStr">
-        <is>
-          <t>% del total</t>
-        </is>
-      </c>
-      <c r="C4" s="7" t="inlineStr">
-        <is>
-          <t>Acción sugerida</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="13" t="inlineStr">
-        <is>
-          <t>Precio</t>
-        </is>
-      </c>
-      <c r="B5" s="21" t="n"/>
-      <c r="C5" s="13" t="inlineStr">
-        <is>
-          <t>Revisar precio, crear plan de pagos</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="13" t="inlineStr">
-        <is>
-          <t>Cambio de colegio</t>
-        </is>
-      </c>
-      <c r="B6" s="21" t="n"/>
-      <c r="C6" s="13" t="inlineStr">
-        <is>
-          <t>Nada (factor externo)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="13" t="inlineStr">
-        <is>
-          <t>Falta de interés de la niña</t>
-        </is>
-      </c>
-      <c r="B7" s="21" t="n"/>
-      <c r="C7" s="13" t="inlineStr">
-        <is>
-          <t>Revisar metodología, añadir variedad</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="13" t="inlineStr">
-        <is>
-          <t>Lesión</t>
-        </is>
-      </c>
-      <c r="B8" s="21" t="n"/>
-      <c r="C8" s="13" t="inlineStr">
-        <is>
-          <t>Revisar protocolo de calentamiento</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="13" t="inlineStr">
-        <is>
-          <t>Horarios incompatibles</t>
-        </is>
-      </c>
-      <c r="B9" s="21" t="n"/>
-      <c r="C9" s="13" t="inlineStr">
-        <is>
-          <t>PRIORIDAD #1: Abrir horarios alternativos</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="13" t="inlineStr">
-        <is>
-          <t>Cambio de ciudad</t>
-        </is>
-      </c>
-      <c r="B10" s="21" t="n"/>
-      <c r="C10" s="13" t="inlineStr">
-        <is>
-          <t>Nada (factor externo)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="13" t="inlineStr">
-        <is>
-          <t>Otra actividad (fútbol, natación)</t>
-        </is>
-      </c>
-      <c r="B11" s="21" t="n"/>
-      <c r="C11" s="13" t="inlineStr">
-        <is>
-          <t>Analizar qué ofrecen esas actividades</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="13" t="inlineStr">
-        <is>
-          <t>Insatisfacción con la enseñanza</t>
-        </is>
-      </c>
-      <c r="B12" s="21" t="n"/>
-      <c r="C12" s="13" t="inlineStr">
-        <is>
-          <t>Revisar metodología</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="13" t="inlineStr">
-        <is>
-          <t>Problemas familiares/económicos</t>
-        </is>
-      </c>
-      <c r="B13" s="21" t="n"/>
-      <c r="C13" s="13" t="inlineStr">
-        <is>
-          <t>Ofrecer plan de emergencia</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="13" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="B14" s="21" t="n"/>
-      <c r="C14" s="13" t="inlineStr">
-        <is>
-          <t>Llamar personalmente a cada familia</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="20" t="inlineStr">
-        <is>
-          <t>5.2 TASA DE ABANDONO MENSUAL</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="7" t="inlineStr">
-        <is>
-          <t>Mes</t>
-        </is>
-      </c>
-      <c r="B18" s="7" t="inlineStr">
-        <is>
-          <t>Alumnas inicio</t>
-        </is>
-      </c>
-      <c r="C18" s="7" t="inlineStr">
-        <is>
-          <t>Alumnas abandonan</t>
-        </is>
-      </c>
-      <c r="D18" s="7" t="inlineStr">
-        <is>
-          <t>Tasa (%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="13" t="inlineStr">
-        <is>
-          <t>Mes 1</t>
-        </is>
-      </c>
-      <c r="B19" s="22" t="n"/>
-      <c r="C19" s="22" t="n"/>
-      <c r="D19" s="23">
-        <f>IF(B19=0,0,C19/B19)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="13" t="inlineStr">
-        <is>
-          <t>Mes 2</t>
-        </is>
-      </c>
-      <c r="B20" s="22" t="n"/>
-      <c r="C20" s="22" t="n"/>
-      <c r="D20" s="23">
-        <f>IF(B20=0,0,C20/B20)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="13" t="inlineStr">
-        <is>
-          <t>Mes 3</t>
-        </is>
-      </c>
-      <c r="B21" s="22" t="n"/>
-      <c r="C21" s="22" t="n"/>
-      <c r="D21" s="23">
-        <f>IF(B21=0,0,C21/B21)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="13" t="inlineStr">
-        <is>
-          <t>Mes 4</t>
-        </is>
-      </c>
-      <c r="B22" s="22" t="n"/>
-      <c r="C22" s="22" t="n"/>
-      <c r="D22" s="23">
-        <f>IF(B22=0,0,C22/B22)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="13" t="inlineStr">
-        <is>
-          <t>Mes 5</t>
-        </is>
-      </c>
-      <c r="B23" s="22" t="n"/>
-      <c r="C23" s="22" t="n"/>
-      <c r="D23" s="23">
-        <f>IF(B23=0,0,C23/B23)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="13" t="inlineStr">
-        <is>
-          <t>Mes 6</t>
-        </is>
-      </c>
-      <c r="B24" s="22" t="n"/>
-      <c r="C24" s="22" t="n"/>
-      <c r="D24" s="23">
-        <f>IF(B24=0,0,C24/B24)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="24" t="inlineStr">
-        <is>
-          <t>⚠️ UMBRAL CRÍTICO: &gt;15% abandono mensual = producto defectuoso</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A26:C26"/>
-    <mergeCell ref="A2:C2"/>
-    <mergeCell ref="A17:C17"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C21"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="35" customWidth="1" min="1" max="1"/>
-    <col width="25" customWidth="1" min="2" max="2"/>
-    <col width="25" customWidth="1" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>BLOQUE 6: SATISFACCIÓN DEL CLIENTE</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="20" t="inlineStr">
-        <is>
-          <t>NPS (NET PROMOTER SCORE) — ENCUESTA TRIMESTRAL</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="7" t="inlineStr">
-        <is>
-          <t>Respuesta</t>
-        </is>
-      </c>
-      <c r="B4" s="7" t="inlineStr">
-        <is>
-          <t>Categoría</t>
-        </is>
-      </c>
-      <c r="C4" s="7" t="inlineStr">
-        <is>
-          <t>Cantidad</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="13" t="inlineStr">
-        <is>
-          <t>0-6</t>
-        </is>
-      </c>
-      <c r="B6" s="13" t="inlineStr">
-        <is>
-          <t>Detractora</t>
-        </is>
-      </c>
-      <c r="C6" s="13" t="n"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="13" t="inlineStr">
-        <is>
-          <t>7-8</t>
-        </is>
-      </c>
-      <c r="B7" s="25" t="inlineStr">
-        <is>
-          <t>Pasiva</t>
-        </is>
-      </c>
-      <c r="C7" s="13" t="n"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="13" t="inlineStr">
-        <is>
-          <t>9-10</t>
-        </is>
-      </c>
-      <c r="B8" s="25" t="inlineStr">
-        <is>
-          <t>Promotora</t>
-        </is>
-      </c>
-      <c r="C8" s="13" t="n"/>
-    </row>
-    <row r="9">
-      <c r="B9" s="26" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="20" t="inlineStr">
-        <is>
-          <t>NPS = % Promotoras - % Detractoras</t>
-        </is>
-      </c>
-      <c r="B10" s="27">
-        <f>(B9/(B7+B8+B9))-(B7/(B7+B8+B9))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="24" t="inlineStr">
-        <is>
-          <t>⚠️ UMBRAL: NPS &gt; 50 = excelente | NPS &lt; 30 = revisar urgente</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="20" t="inlineStr">
-        <is>
-          <t>TESTIMONIOS RECOPILADOS</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="7" t="inlineStr">
-        <is>
-          <t>Fecha</t>
-        </is>
-      </c>
-      <c r="B16" s="7" t="inlineStr">
-        <is>
-          <t>Testimonio (iniciales)</t>
-        </is>
-      </c>
-      <c r="C16" s="7" t="inlineStr">
-        <is>
-          <t>Usado en marketing</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="22" t="n"/>
-      <c r="B17" s="22" t="n"/>
-      <c r="C17" s="22" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="22" t="n"/>
-      <c r="B18" s="22" t="n"/>
-      <c r="C18" s="22" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="22" t="n"/>
-      <c r="B19" s="22" t="n"/>
-      <c r="C19" s="22" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="22" t="n"/>
-      <c r="B20" s="22" t="n"/>
-      <c r="C20" s="22" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="22" t="n"/>
-      <c r="B21" s="22" t="n"/>
-      <c r="C21" s="22" t="n"/>
-    </row>
-  </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A3:C3"/>
-    <mergeCell ref="A12:C12"/>
-    <mergeCell ref="A15:C15"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B9"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>BLOQUE 9: ANÁLISIS DAFO</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="28" t="inlineStr">
-        <is>
-          <t>FORTALEZAS</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="29" t="inlineStr">
-        <is>
-          <t>DEBILIDADES</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="30" t="inlineStr">
-        <is>
-          <t>OPORTUNIDADES</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="31" t="inlineStr">
-        <is>
-          <t>AMENAZAS</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="5">
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="A9:B9"/>
-    <mergeCell ref="A3:B3"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C10"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="25" customWidth="1" min="2" max="2"/>
-    <col width="35" customWidth="1" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>BLOQUE 11: CANALES DE ADQUISICIÓN</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="7" t="inlineStr">
-        <is>
-          <t>Canal</t>
-        </is>
-      </c>
-      <c r="B3" s="7" t="inlineStr">
-        <is>
-          <t>Fuerza en Mérida</t>
-        </is>
-      </c>
-      <c r="C3" s="7" t="inlineStr">
-        <is>
-          <t>¿Cómo medir?</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="13" t="inlineStr">
-        <is>
-          <t>Recomendación madre-madre</t>
-        </is>
-      </c>
-      <c r="B4" s="13" t="inlineStr">
-        <is>
-          <t>🔴 ALTA</t>
-        </is>
-      </c>
-      <c r="C4" s="13" t="inlineStr">
-        <is>
-          <t>Encuesta: ¿Cómo se enteró?</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="13" t="inlineStr">
-        <is>
-          <t>Colegios</t>
-        </is>
-      </c>
-      <c r="B5" s="13" t="inlineStr">
-        <is>
-          <t>🔴 ALTA</t>
-        </is>
-      </c>
-      <c r="C5" s="13" t="inlineStr">
-        <is>
-          <t>¿Alianzas activas? ¿Panfletos?</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="13" t="inlineStr">
-        <is>
-          <t>Grupos WhatsApp de padres</t>
-        </is>
-      </c>
-      <c r="B6" s="13" t="inlineStr">
-        <is>
-          <t>🔴 ALTA</t>
-        </is>
-      </c>
-      <c r="C6" s="13" t="inlineStr">
-        <is>
-          <t>¿Aparece en conversaciones?</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="13" t="inlineStr">
-        <is>
-          <t>Instagram local</t>
-        </is>
-      </c>
-      <c r="B7" s="13" t="inlineStr">
-        <is>
-          <t>🟡 MEDIA</t>
-        </is>
-      </c>
-      <c r="C7" s="13" t="inlineStr">
-        <is>
-          <t>Seguidores, interacción, DMs</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="13" t="inlineStr">
-        <is>
-          <t>Eventos gratuitos / muestras</t>
-        </is>
-      </c>
-      <c r="B8" s="13" t="inlineStr">
-        <is>
-          <t>🟡 MEDIA</t>
-        </is>
-      </c>
-      <c r="C8" s="13" t="inlineStr">
-        <is>
-          <t>Asistencia, conversión</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="13" t="inlineStr">
-        <is>
-          <t>Meta Ads pagadas</t>
-        </is>
-      </c>
-      <c r="B9" s="13" t="inlineStr">
-        <is>
-          <t>🟢 BAJA</t>
-        </is>
-      </c>
-      <c r="C9" s="13" t="inlineStr">
-        <is>
-          <t>CAC probablemente &gt; LTV</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="13" t="inlineStr">
-        <is>
-          <t>Pasear por el local</t>
-        </is>
-      </c>
-      <c r="B10" s="13" t="inlineStr">
-        <is>
-          <t>🟢 BAJA-MEDIA</t>
-        </is>
-      </c>
-      <c r="C10" s="13" t="inlineStr">
-        <is>
-          <t>¿Cuántos entran por el letrero?</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:C1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C8"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="35" customWidth="1" min="1" max="1"/>
-    <col width="45" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>BLOQUE 12: EXPERIMENTOS DE VALIDACIÓN</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="13" t="inlineStr">
-        <is>
-          <t>Exp 1: Observación competencia</t>
-        </is>
-      </c>
-      <c r="B3" s="13" t="inlineStr">
-        <is>
-          <t>0 USD, 3-4 días</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>Contar entradas en Nueva Danza y Agbara</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="13" t="inlineStr">
-        <is>
-          <t>Exp 2: Entrevistas interceptación</t>
-        </is>
-      </c>
-      <c r="B4" s="13" t="inlineStr">
-        <is>
-          <t>0 USD, 3-5 días</t>
-        </is>
-      </c>
-      <c r="C4" s="13" t="inlineStr">
-        <is>
-          <t>Objetivo: 20+ contactos WhatsApp</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="13" t="inlineStr">
-        <is>
-          <t>Exp 3: Test de precio</t>
-        </is>
-      </c>
-      <c r="B5" s="13" t="inlineStr">
-        <is>
-          <t>Interno</t>
-        </is>
-      </c>
-      <c r="C5" s="13" t="inlineStr">
-        <is>
-          <t>Subir 10-15% a nuevas. ¿Baja conversión?</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="13" t="inlineStr">
-        <is>
-          <t>Exp 4: Oferta premium (Danza Chic Elite)</t>
-        </is>
-      </c>
-      <c r="B6" s="13" t="inlineStr">
-        <is>
-          <t>0 USD</t>
-        </is>
-      </c>
-      <c r="C6" s="13" t="inlineStr">
-        <is>
-          <t>Medir % familias que pagan upgrade</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="13" t="inlineStr">
-        <is>
-          <t>Exp 5: Sistema de referidos</t>
-        </is>
-      </c>
-      <c r="B7" s="13" t="inlineStr">
-        <is>
-          <t>Costo bajo</t>
-        </is>
-      </c>
-      <c r="C7" s="13" t="inlineStr">
-        <is>
-          <t>1 semana gratis por referida</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="13" t="inlineStr">
-        <is>
-          <t>Exp 6: Pop-up (MVP)</t>
-        </is>
-      </c>
-      <c r="B8" s="13" t="inlineStr">
-        <is>
-          <t>100-300 USD</t>
-        </is>
-      </c>
-      <c r="C8" s="13" t="inlineStr">
-        <is>
-          <t>Alquilar sala 8 semanas. Objetivo: 30 alumnas</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:C1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>